--- a/public/cost-template.xlsx
+++ b/public/cost-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaquibfaridi/Desktop/Aaquib/cpcompliance/frontend/src/components/Protected/Sites/EnergyCost/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaquibfaridi/Desktop/Aaquib/cpcompliance/frontend/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6188F350-8407-6F47-A477-24647F407D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C581499-59B9-C04B-87FD-07187ADAD49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16340" xr2:uid="{8B632CFA-6A58-9A49-9EAD-C6A770500F9B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>From Date (DD/MM/YYYY)</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>Cost (GBP)</t>
+  </si>
+  <si>
+    <t>Reference</t>
   </si>
 </sst>
 </file>
@@ -80,16 +83,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -107,12 +130,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}" name="Table2" displayName="Table2" ref="A1:C1048576" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:C1048576" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="From Date (DD/MM/YYYY)"/>
-    <tableColumn id="2" xr3:uid="{6F160CE5-9BF6-2A40-BF8D-DA6CC5EF89C8}" name="To Date (DD/MM/YYYY)"/>
-    <tableColumn id="3" xr3:uid="{3ED0B6B4-0EF1-7849-8940-4D8CF2183B14}" name="Cost (GBP)"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}" name="Table2" displayName="Table2" ref="A1:D1048576" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:D1048576" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}"/>
+  <tableColumns count="4">
+    <tableColumn id="4" xr3:uid="{B8B97D3D-2174-5642-B57A-5B26E2D62831}" name="Reference" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="From Date (DD/MM/YYYY)" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{6F160CE5-9BF6-2A40-BF8D-DA6CC5EF89C8}" name="To Date (DD/MM/YYYY)" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{3ED0B6B4-0EF1-7849-8940-4D8CF2183B14}" name="Cost (GBP)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -435,22 +459,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C961255-8D4E-8445-9D9B-F5A2E3A7180D}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="46.1640625" customWidth="1"/>
-    <col min="3" max="3" width="62.6640625" customWidth="1"/>
+    <col min="1" max="2" width="40" style="3" customWidth="1"/>
+    <col min="3" max="3" width="46.1640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="62.6640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
     </row>

--- a/public/cost-template.xlsx
+++ b/public/cost-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaquibfaridi/Desktop/Aaquib/cpcompliance/frontend/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C581499-59B9-C04B-87FD-07187ADAD49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A76F17-E80F-5447-9451-C41B1F622760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16340" xr2:uid="{8B632CFA-6A58-9A49-9EAD-C6A770500F9B}"/>
   </bookViews>
@@ -38,16 +38,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>From Date (DD/MM/YYYY)</t>
-  </si>
-  <si>
-    <t>To Date (DD/MM/YYYY)</t>
-  </si>
-  <si>
     <t>Cost (GBP)</t>
   </si>
   <si>
     <t>Reference</t>
+  </si>
+  <si>
+    <t>From Date (YYYY/MM/DD)</t>
+  </si>
+  <si>
+    <t>To Date (YYYY/MM/DD)</t>
   </si>
 </sst>
 </file>
@@ -88,14 +88,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -105,10 +105,10 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -134,8 +134,8 @@
   <autoFilter ref="A1:D1048576" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}"/>
   <tableColumns count="4">
     <tableColumn id="4" xr3:uid="{B8B97D3D-2174-5642-B57A-5B26E2D62831}" name="Reference" dataDxfId="3"/>
-    <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="From Date (DD/MM/YYYY)" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{6F160CE5-9BF6-2A40-BF8D-DA6CC5EF89C8}" name="To Date (DD/MM/YYYY)" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="From Date (YYYY/MM/DD)" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{6F160CE5-9BF6-2A40-BF8D-DA6CC5EF89C8}" name="To Date (YYYY/MM/DD)" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{3ED0B6B4-0EF1-7849-8940-4D8CF2183B14}" name="Cost (GBP)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -462,23 +462,24 @@
   <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="40" style="3" customWidth="1"/>
-    <col min="3" max="3" width="46.1640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="62.6640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="40" style="5" customWidth="1"/>
+    <col min="3" max="3" width="46.1640625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="62.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/public/cost-template.xlsx
+++ b/public/cost-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaquibfaridi/Desktop/Aaquib/cpcompliance/frontend/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaquibfaridi\Downloads\tdk\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A76F17-E80F-5447-9451-C41B1F622760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C264C7F-0264-4058-B97A-5C78F5D45F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16340" xr2:uid="{8B632CFA-6A58-9A49-9EAD-C6A770500F9B}"/>
+    <workbookView xWindow="3490" yWindow="2720" windowWidth="15710" windowHeight="7360" xr2:uid="{8B632CFA-6A58-9A49-9EAD-C6A770500F9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,13 +41,13 @@
     <t>Cost (GBP)</t>
   </si>
   <si>
-    <t>Reference</t>
+    <t>To Date (YYYY/MM/DD)</t>
   </si>
   <si>
-    <t>From Date (YYYY/MM/DD)</t>
+    <t>From Date (DD/MM/YYYY)</t>
   </si>
   <si>
-    <t>To Date (YYYY/MM/DD)</t>
+    <t>Meter Reference</t>
   </si>
 </sst>
 </file>
@@ -133,8 +133,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}" name="Table2" displayName="Table2" ref="A1:D1048576" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A1:D1048576" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{B8B97D3D-2174-5642-B57A-5B26E2D62831}" name="Reference" dataDxfId="3"/>
-    <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="From Date (YYYY/MM/DD)" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{B8B97D3D-2174-5642-B57A-5B26E2D62831}" name="Meter Reference" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="From Date (DD/MM/YYYY)" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{6F160CE5-9BF6-2A40-BF8D-DA6CC5EF89C8}" name="To Date (YYYY/MM/DD)" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{3ED0B6B4-0EF1-7849-8940-4D8CF2183B14}" name="Cost (GBP)" dataDxfId="0"/>
   </tableColumns>
@@ -460,7 +460,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C961255-8D4E-8445-9D9B-F5A2E3A7180D}">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="40" style="5" customWidth="1"/>
@@ -468,15 +468,15 @@
     <col min="4" max="4" width="62.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>

--- a/public/cost-template.xlsx
+++ b/public/cost-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaquibfaridi\Downloads\tdk\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C264C7F-0264-4058-B97A-5C78F5D45F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB398BE4-114B-43CA-A53B-A1822BDF625D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3490" yWindow="2720" windowWidth="15710" windowHeight="7360" xr2:uid="{8B632CFA-6A58-9A49-9EAD-C6A770500F9B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8B632CFA-6A58-9A49-9EAD-C6A770500F9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,13 +41,13 @@
     <t>Cost (GBP)</t>
   </si>
   <si>
-    <t>To Date (YYYY/MM/DD)</t>
-  </si>
-  <si>
     <t>From Date (DD/MM/YYYY)</t>
   </si>
   <si>
     <t>Meter Reference</t>
+  </si>
+  <si>
+    <t>To Date (DD/MM/YYYY)</t>
   </si>
 </sst>
 </file>
@@ -135,7 +135,7 @@
   <tableColumns count="4">
     <tableColumn id="4" xr3:uid="{B8B97D3D-2174-5642-B57A-5B26E2D62831}" name="Meter Reference" dataDxfId="3"/>
     <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="From Date (DD/MM/YYYY)" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{6F160CE5-9BF6-2A40-BF8D-DA6CC5EF89C8}" name="To Date (YYYY/MM/DD)" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{6F160CE5-9BF6-2A40-BF8D-DA6CC5EF89C8}" name="To Date (DD/MM/YYYY)" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{3ED0B6B4-0EF1-7849-8940-4D8CF2183B14}" name="Cost (GBP)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -470,13 +470,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>

--- a/public/cost-template.xlsx
+++ b/public/cost-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaquibfaridi\Downloads\tdk\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB398BE4-114B-43CA-A53B-A1822BDF625D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9654195E-D80F-4ED7-9BE0-A7F914606046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8B632CFA-6A58-9A49-9EAD-C6A770500F9B}"/>
   </bookViews>
@@ -463,9 +463,9 @@
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="40" style="5" customWidth="1"/>
-    <col min="3" max="3" width="46.1640625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="62.6640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="25.75" style="5" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.4">
